--- a/SQL/PostgreSQL/Projeto Controle Red Ribbon/Controle FInaceiro RedRibbon2026.xlsx
+++ b/SQL/PostgreSQL/Projeto Controle Red Ribbon/Controle FInaceiro RedRibbon2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\biblioteca\Projetos 2026\projetinho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\biblioteca\Projetos 2026\Estudos Iniciais\Estudo de dados\SQL\PostgreSQL\Projeto Controle Red Ribbon\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="49">
   <si>
     <t>ENTRADAS</t>
   </si>
@@ -1604,13 +1604,21 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
+      <c r="C12" s="13">
+        <v>46160</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="15">
+        <v>18</v>
+      </c>
       <c r="G12" s="10" t="str">
         <f>IF(E12="", "", IF(COUNTIF('Aba 2'!$A$5:$A$7, E12)&gt;0, "Entrada", IF(COUNTIF('Aba 2'!$A$11:$A$15, E12)&gt;0, "Saída", "Investimento")))</f>
-        <v/>
+        <v>Investimento</v>
       </c>
       <c r="H12" s="16"/>
     </row>
